--- a/data/processed/harmonization/Carbon__Dissolved_organic_carbon/10.15485_1960313/10.15485_1960313_soil_Carbon__Dissolved_organic_carbon.xlsx
+++ b/data/processed/harmonization/Carbon__Dissolved_organic_carbon/10.15485_1960313/10.15485_1960313_soil_Carbon__Dissolved_organic_carbon.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
@@ -530,12 +530,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>IEEXG001D</t>
+          <t>water:IEEXG001D</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -592,12 +592,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0035</t>
+          <t>water:IEEXG0035</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -654,12 +654,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>IEEXG003L</t>
+          <t>water:IEEXG003L</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0041</t>
+          <t>water:IEEXG0041</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -778,12 +778,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>IEEXG004H</t>
+          <t>water:IEEXG004H</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -840,12 +840,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>IEEXG004X</t>
+          <t>water:IEEXG004X</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -902,12 +902,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>IEEXG005D</t>
+          <t>water:IEEXG005D</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -964,12 +964,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0069</t>
+          <t>water:IEEXG0069</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>IEEXG006P</t>
+          <t>water:IEEXG006P</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0075</t>
+          <t>water:IEEXG0075</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>IEEXG007L</t>
+          <t>water:IEEXG007L</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0081</t>
+          <t>water:IEEXG0081</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>IEEXG008H</t>
+          <t>water:IEEXG008H</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>IEEXG008X</t>
+          <t>water:IEEXG008X</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>IEEXG009D</t>
+          <t>water:IEEXG009D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>IEEXG009T</t>
+          <t>water:IEEXG009T</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00A9</t>
+          <t>water:IEEXG00A9</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1584,12 +1584,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00AP</t>
+          <t>water:IEEXG00AP</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00B5</t>
+          <t>water:IEEXG00B5</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1708,12 +1708,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00CH</t>
+          <t>water:IEEXG00CH</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00CX</t>
+          <t>water:IEEXG00CX</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00E9</t>
+          <t>water:IEEXG00E9</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -1894,12 +1894,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00EP</t>
+          <t>water:IEEXG00EP</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1956,12 +1956,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00F5</t>
+          <t>water:IEEXG00F5</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -2018,12 +2018,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00FL</t>
+          <t>water:IEEXG00FL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -2080,12 +2080,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00G1</t>
+          <t>water:IEEXG00G1</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00GH</t>
+          <t>water:IEEXG00GH</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00GX</t>
+          <t>water:IEEXG00GX</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00HD</t>
+          <t>water:IEEXG00HD</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00HT</t>
+          <t>water:IEEXG00HT</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00I9</t>
+          <t>water:IEEXG00I9</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -2452,12 +2452,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00IP</t>
+          <t>water:IEEXG00IP</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -2514,12 +2514,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00J5</t>
+          <t>water:IEEXG00J5</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00JL</t>
+          <t>water:IEEXG00JL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -2638,12 +2638,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00K1</t>
+          <t>water:IEEXG00K1</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -2700,12 +2700,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00KH</t>
+          <t>water:IEEXG00KH</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -2762,12 +2762,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00KX</t>
+          <t>water:IEEXG00KX</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -2824,12 +2824,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00LD</t>
+          <t>water:IEEXG00LD</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -2886,12 +2886,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00LT</t>
+          <t>water:IEEXG00LT</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -2948,12 +2948,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00M9</t>
+          <t>water:IEEXG00M9</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00MP</t>
+          <t>water:IEEXG00MP</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -3072,12 +3072,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00N5</t>
+          <t>water:IEEXG00N5</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00NL</t>
+          <t>water:IEEXG00NL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00O1</t>
+          <t>water:IEEXG00O1</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -3258,12 +3258,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00OH</t>
+          <t>water:IEEXG00OH</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -3320,12 +3320,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00PD</t>
+          <t>water:IEEXG00PD</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -3382,12 +3382,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00PT</t>
+          <t>water:IEEXG00PT</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -3444,12 +3444,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00Q9</t>
+          <t>water:IEEXG00Q9</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -3506,12 +3506,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00QP</t>
+          <t>water:IEEXG00QP</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -3568,12 +3568,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00R5</t>
+          <t>water:IEEXG00R5</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
